--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PROINBENI UPB GANDIA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>126.663</v>
+        <v>131.3688</v>
       </c>
       <c r="E2" t="n">
-        <v>113.0967</v>
+        <v>114.8946</v>
       </c>
       <c r="F2" t="n">
-        <v>13.5663</v>
+        <v>16.4741</v>
       </c>
       <c r="G2" t="n">
         <v>55.9518</v>
@@ -610,13 +610,13 @@
         <v>57.7009</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.977</v>
+        <v>0.7289000000000003</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.639</v>
+        <v>-1.8412</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3379</v>
+        <v>2.57</v>
       </c>
       <c r="V2" t="n">
         <v>57.645</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>53.142</v>
+        <v>42.3941</v>
       </c>
       <c r="E3" t="n">
-        <v>29.8586</v>
+        <v>20.3596</v>
       </c>
       <c r="F3" t="n">
-        <v>23.2828</v>
+        <v>22.0345</v>
       </c>
       <c r="G3" t="n">
         <v>15.3784</v>
@@ -688,13 +688,13 @@
         <v>50.7195</v>
       </c>
       <c r="S3" t="n">
-        <v>16.9125</v>
+        <v>6.1645</v>
       </c>
       <c r="T3" t="n">
-        <v>10.7306</v>
+        <v>1.2315</v>
       </c>
       <c r="U3" t="n">
-        <v>6.1816</v>
+        <v>4.9329</v>
       </c>
       <c r="V3" t="n">
         <v>11.6106</v>
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>26.9462</v>
+        <v>32.9786</v>
       </c>
       <c r="E4" t="n">
-        <v>16.2801</v>
+        <v>18.9262</v>
       </c>
       <c r="F4" t="n">
-        <v>10.6658</v>
+        <v>14.0524</v>
       </c>
       <c r="G4" t="n">
         <v>7.063099999999999</v>
@@ -766,13 +766,13 @@
         <v>46.2019</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.8567</v>
+        <v>-0.8239999999999997</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.776199999999999</v>
+        <v>-4.13</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08049999999999979</v>
+        <v>3.3058</v>
       </c>
       <c r="V4" t="n">
         <v>1.8933</v>
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7637</v>
+        <v>11.2438</v>
       </c>
       <c r="E5" t="n">
-        <v>7.387899999999999</v>
+        <v>11.5646</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6242000000000001</v>
+        <v>-0.3205999999999996</v>
       </c>
       <c r="G5" t="n">
         <v>12.1631</v>
@@ -844,13 +844,13 @@
         <v>50.1036</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.2916</v>
+        <v>-2.8112</v>
       </c>
       <c r="T5" t="n">
-        <v>-6.536199999999999</v>
+        <v>-2.3596</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7552999999999997</v>
+        <v>-0.4520000000000002</v>
       </c>
       <c r="V5" t="n">
         <v>-22.9541</v>
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>5.358900000000001</v>
+        <v>8.9626</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.6817</v>
+        <v>-4.8293</v>
       </c>
       <c r="F6" t="n">
-        <v>11.0407</v>
+        <v>13.7922</v>
       </c>
       <c r="G6" t="n">
         <v>2.236199999999999</v>
@@ -922,13 +922,13 @@
         <v>24.8464</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.9268</v>
+        <v>-1.3231</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.9586</v>
+        <v>-1.1063</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.9684</v>
+        <v>-0.217</v>
       </c>
       <c r="V6" t="n">
         <v>-3.2439</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.090500000000002</v>
+        <v>1.288</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9957999999999984</v>
+        <v>-3.3443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09459999999999957</v>
+        <v>4.632099999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.818099999999999</v>
+        <v>17.6183</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4071</v>
+        <v>2.7037</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.2252</v>
+        <v>14.9145</v>
       </c>
       <c r="J7" t="n">
-        <v>16.7285</v>
+        <v>37.1574</v>
       </c>
       <c r="K7" t="n">
-        <v>13.1648</v>
+        <v>12.6535</v>
       </c>
       <c r="L7" t="n">
-        <v>3.5633</v>
+        <v>24.5039</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.5466</v>
+        <v>-19.5392</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.758</v>
+        <v>-9.9499</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.7887</v>
+        <v>-9.589499999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8484</v>
+        <v>-11.9099</v>
       </c>
       <c r="Q7" t="n">
-        <v>-33.4706</v>
+        <v>-60.781</v>
       </c>
       <c r="R7" t="n">
-        <v>35.3192</v>
+        <v>48.8712</v>
       </c>
       <c r="S7" t="n">
-        <v>16.172</v>
+        <v>0.6033000000000005</v>
       </c>
       <c r="T7" t="n">
-        <v>15.2458</v>
+        <v>-1.2435</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9261</v>
+        <v>1.8467</v>
       </c>
       <c r="V7" t="n">
-        <v>-12.1115</v>
+        <v>-5.0237</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4923</v>
+        <v>21.5231</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.6038</v>
+        <v>-26.547</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.641</v>
+        <v>-0.3066</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.331</v>
+        <v>-0.05589999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3099999999999999</v>
+        <v>-0.2507</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4169</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.224</v>
+        <v>0.1104</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2635</v>
+        <v>0.0116</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.852300000000001</v>
+        <v>-0.4519000000000009</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.4673</v>
+        <v>-0.8513999999999996</v>
       </c>
       <c r="F9" t="n">
-        <v>4.6151</v>
+        <v>0.3997999999999995</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.0648</v>
+        <v>-9.0959</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.547499999999999</v>
+        <v>-11.384</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4825</v>
+        <v>2.2881</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4397</v>
+        <v>12.5648</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1374</v>
+        <v>2.5092</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5773</v>
+        <v>10.0557</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.5047</v>
+        <v>-21.6607</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.4101</v>
+        <v>-13.8931</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0945</v>
+        <v>-7.7677</v>
       </c>
       <c r="P9" t="n">
-        <v>-13.5525</v>
+        <v>-9.0349</v>
       </c>
       <c r="Q9" t="n">
-        <v>-30.8011</v>
+        <v>-43.5322</v>
       </c>
       <c r="R9" t="n">
-        <v>17.2487</v>
+        <v>34.4978</v>
       </c>
       <c r="S9" t="n">
-        <v>7.7104</v>
+        <v>-7.2931</v>
       </c>
       <c r="T9" t="n">
-        <v>4.7444</v>
+        <v>-5.4191</v>
       </c>
       <c r="U9" t="n">
-        <v>2.966</v>
+        <v>-1.874</v>
       </c>
       <c r="V9" t="n">
-        <v>10.0545</v>
+        <v>24.9725</v>
       </c>
       <c r="W9" t="n">
-        <v>15.1494</v>
+        <v>35.5351</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.0951</v>
+        <v>-10.5625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OSAIKHWUWUOMWAN</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4746</v>
+        <v>-0.8679999999999992</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0062</v>
+        <v>-7.1901</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4684</v>
+        <v>6.321999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-10.2118</v>
+        <v>2.744300000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9892</v>
+        <v>-4.8489</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.2226</v>
+        <v>7.593</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8069</v>
+        <v>10.8249</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5227</v>
+        <v>2.0547</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.329800000000001</v>
+        <v>8.770399999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.404999999999999</v>
+        <v>-8.0806</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.512</v>
+        <v>-6.9036</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.8929</v>
+        <v>-1.1771</v>
       </c>
       <c r="P10" t="n">
-        <v>5.5443</v>
+        <v>-6.5709</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-35.1132</v>
       </c>
       <c r="R10" t="n">
-        <v>8.6244</v>
+        <v>28.5428</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1884999999999999</v>
+        <v>-0.08000000000000014</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8952</v>
+        <v>-1.8272</v>
       </c>
       <c r="U10" t="n">
-        <v>2.0837</v>
+        <v>1.7469</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9953000000000004</v>
+        <v>3.038799999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7761</v>
+        <v>18.9256</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.7714</v>
+        <v>-15.8866</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>C. OSAIKHWUWUOMWAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.188000000000001</v>
+        <v>-5.4229</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.3705</v>
+        <v>-3.2081</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1826</v>
+        <v>-2.2149</v>
       </c>
       <c r="G11" t="n">
-        <v>2.744300000000002</v>
+        <v>-10.2118</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.8489</v>
+        <v>-1.9892</v>
       </c>
       <c r="I11" t="n">
-        <v>7.593</v>
+        <v>-8.2226</v>
       </c>
       <c r="J11" t="n">
-        <v>10.8249</v>
+        <v>-2.8069</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0547</v>
+        <v>1.5227</v>
       </c>
       <c r="L11" t="n">
-        <v>8.770399999999999</v>
+        <v>-4.329800000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.0806</v>
+        <v>-7.404999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.9036</v>
+        <v>-3.512</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1771</v>
+        <v>-3.8929</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.5709</v>
+        <v>5.5443</v>
       </c>
       <c r="Q11" t="n">
-        <v>-35.1132</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>28.5428</v>
+        <v>8.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.4001</v>
+        <v>0.2402000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.0078</v>
+        <v>-1.0973</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3922000000000003</v>
+        <v>1.3373</v>
       </c>
       <c r="V11" t="n">
-        <v>3.038799999999999</v>
+        <v>-0.9953000000000004</v>
       </c>
       <c r="W11" t="n">
-        <v>18.9256</v>
+        <v>3.7761</v>
       </c>
       <c r="X11" t="n">
-        <v>-15.8866</v>
+        <v>-4.7714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.802899999999999</v>
+        <v>-6.880600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.0105</v>
+        <v>-8.3369</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2075</v>
+        <v>1.4563</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.517999999999999</v>
+        <v>-4.818099999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9606</v>
+        <v>1.4071</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.557099999999999</v>
+        <v>-6.2252</v>
       </c>
       <c r="J12" t="n">
-        <v>7.760400000000001</v>
+        <v>16.7285</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7637</v>
+        <v>13.1648</v>
       </c>
       <c r="L12" t="n">
-        <v>4.9969</v>
+        <v>3.5633</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.2783</v>
+        <v>-21.5466</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.724</v>
+        <v>-11.758</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.5541</v>
+        <v>-9.7887</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0267</v>
+        <v>1.8484</v>
       </c>
       <c r="Q12" t="n">
-        <v>-29.5692</v>
+        <v>-33.4706</v>
       </c>
       <c r="R12" t="n">
-        <v>30.5959</v>
+        <v>35.3192</v>
       </c>
       <c r="S12" t="n">
-        <v>7.9529</v>
+        <v>8.200699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>4.913899999999999</v>
+        <v>5.9132</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0395</v>
+        <v>2.2878</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.264699999999999</v>
+        <v>-12.1115</v>
       </c>
       <c r="W12" t="n">
-        <v>8.8847</v>
+        <v>2.4923</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.1495</v>
+        <v>-14.6038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BARBER TERRADES</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.306000000000001</v>
+        <v>-8.3286</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.81</v>
+        <v>-11.8921</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4961</v>
+        <v>3.5634</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8411</v>
+        <v>-8.0648</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.454</v>
+        <v>-9.547499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3869999999999999</v>
+        <v>1.4825</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2312</v>
+        <v>2.4397</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.402</v>
+        <v>-2.1374</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8292</v>
+        <v>4.5773</v>
       </c>
       <c r="M13" t="n">
-        <v>0.39</v>
+        <v>-10.5047</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05220000000000002</v>
+        <v>-7.4101</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4421</v>
+        <v>-3.0945</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.3389</v>
+        <v>-13.5525</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.1602</v>
+        <v>-30.8011</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8213</v>
+        <v>17.2487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7686999999999999</v>
+        <v>3.2341</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6588000000000001</v>
+        <v>1.3198</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1099</v>
+        <v>1.9145</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3572</v>
+        <v>10.0545</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>15.1494</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.5975</v>
+        <v>-5.0951</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>J. BARBER TERRADES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.1245</v>
+        <v>-8.814299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.5688</v>
+        <v>-7.4962</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.5556</v>
+        <v>-1.3182</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.0959</v>
+        <v>-0.8411</v>
       </c>
       <c r="H14" t="n">
-        <v>-11.384</v>
+        <v>-0.454</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2881</v>
+        <v>-0.3869999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>12.5648</v>
+        <v>-1.2312</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5092</v>
+        <v>-0.402</v>
       </c>
       <c r="L14" t="n">
-        <v>10.0557</v>
+        <v>-0.8292</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.6607</v>
+        <v>0.39</v>
       </c>
       <c r="N14" t="n">
-        <v>-13.8931</v>
+        <v>-0.05220000000000002</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.7677</v>
+        <v>0.4421</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.0349</v>
+        <v>-5.3389</v>
       </c>
       <c r="Q14" t="n">
-        <v>-43.5322</v>
+        <v>-6.1602</v>
       </c>
       <c r="R14" t="n">
-        <v>34.4978</v>
+        <v>0.8213</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.9661</v>
+        <v>-0.277</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.1365</v>
+        <v>-0.345</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.8294</v>
+        <v>0.0678</v>
       </c>
       <c r="V14" t="n">
-        <v>24.9725</v>
+        <v>-2.3572</v>
       </c>
       <c r="W14" t="n">
-        <v>35.5351</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.5625</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.5423</v>
+        <v>-10.8404</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.8627</v>
+        <v>-11.6674</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3202999999999994</v>
+        <v>0.8270999999999997</v>
       </c>
       <c r="G15" t="n">
-        <v>17.6183</v>
+        <v>-8.517999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7037</v>
+        <v>-1.9606</v>
       </c>
       <c r="I15" t="n">
-        <v>14.9145</v>
+        <v>-6.557099999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>37.1574</v>
+        <v>7.760400000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>12.6535</v>
+        <v>2.7637</v>
       </c>
       <c r="L15" t="n">
-        <v>24.5039</v>
+        <v>4.9969</v>
       </c>
       <c r="M15" t="n">
-        <v>-19.5392</v>
+        <v>-16.2783</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.9499</v>
+        <v>-4.724</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.589499999999999</v>
+        <v>-11.5541</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.9099</v>
+        <v>1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>-60.781</v>
+        <v>-29.5692</v>
       </c>
       <c r="R15" t="n">
-        <v>48.8712</v>
+        <v>30.5959</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.2271</v>
+        <v>3.9154</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.7621</v>
+        <v>1.2567</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.4649</v>
+        <v>2.6585</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.0237</v>
+        <v>-7.264699999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>21.5231</v>
+        <v>8.8847</v>
       </c>
       <c r="X15" t="n">
-        <v>-26.547</v>
+        <v>-16.1495</v>
       </c>
     </row>
     <row r="16">
@@ -1657,25 +1657,25 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>161.0327</v>
+        <v>186.3226</v>
       </c>
       <c r="E16" t="n">
-        <v>100.5104</v>
+        <v>106.8733</v>
       </c>
       <c r="F16" t="n">
-        <v>60.52139999999999</v>
+        <v>79.4495</v>
       </c>
       <c r="G16" t="n">
         <v>71.18859999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>20.9062</v>
+        <v>20.90620000000001</v>
       </c>
       <c r="I16" t="n">
         <v>50.282</v>
       </c>
       <c r="J16" t="n">
-        <v>281.7113</v>
+        <v>281.7113000000001</v>
       </c>
       <c r="K16" t="n">
         <v>143.518</v>
@@ -1693,25 +1693,25 @@
         <v>-87.91210000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>49.28240000000001</v>
+        <v>49.28239999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-385.0140999999999</v>
+        <v>-385.0141</v>
       </c>
       <c r="R16" t="n">
         <v>434.2989</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.7018</v>
+        <v>10.5891</v>
       </c>
       <c r="T16" t="n">
-        <v>-15.9992</v>
+        <v>-9.636400000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2979</v>
+        <v>20.224</v>
       </c>
       <c r="V16" t="n">
-        <v>55.26430000000001</v>
+        <v>55.26429999999999</v>
       </c>
       <c r="W16" t="n">
         <v>219.8131</v>
